--- a/artfynd/A 59894-2022 artfynd.xlsx
+++ b/artfynd/A 59894-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 59894-2022 artfynd.xlsx
+++ b/artfynd/A 59894-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -981,6 +981,223 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135227137</v>
+      </c>
+      <c r="B5" t="n">
+        <v>108368</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221530</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Hampflockel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Eupatorium cannabinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sandhem, Sandhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>520697</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6363469</v>
+      </c>
+      <c r="S5" t="n">
+        <v>14</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ingela Carlström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ingela Carlström, Tommy Carlström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135230479</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101425</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>224913</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vanlig backsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pulsatilla vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sandhem 180 m SO, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>520737</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6363473</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>F-Vet-1618</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2010-05-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2010-06-30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ingela Carlström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jakob Wilhelmsson, Lars-Erik Eknäs</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59894-2022 artfynd.xlsx
+++ b/artfynd/A 59894-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134722602</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94651583</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134722615</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1082,6 +1102,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135227137</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,8 +1222,20 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135230479</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 59894-2022 artfynd.xlsx
+++ b/artfynd/A 59894-2022 artfynd.xlsx
@@ -1006,7 +1006,7 @@
         <v>135227137</v>
       </c>
       <c r="B5" t="n">
-        <v>108368</v>
+        <v>108424</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>135230479</v>
       </c>
       <c r="B6" t="n">
-        <v>101425</v>
+        <v>101473</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 59894-2022 artfynd.xlsx
+++ b/artfynd/A 59894-2022 artfynd.xlsx
@@ -1006,7 +1006,7 @@
         <v>135227137</v>
       </c>
       <c r="B5" t="n">
-        <v>108424</v>
+        <v>108451</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>135230479</v>
       </c>
       <c r="B6" t="n">
-        <v>101473</v>
+        <v>101500</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 59894-2022 artfynd.xlsx
+++ b/artfynd/A 59894-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -998,6 +998,233 @@
       <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134722615</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135227137</v>
+      </c>
+      <c r="B5" t="n">
+        <v>108456</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221530</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Hampflockel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Eupatorium cannabinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sandhem, Sandhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>520697</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6363469</v>
+      </c>
+      <c r="S5" t="n">
+        <v>14</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ingela Carlström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tommy Carlström, Ingela Carlström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135227137</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135230479</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101505</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>224913</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vanlig backsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pulsatilla vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sandhem 180 m SO, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>520737</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6363473</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>F-Vet-1618</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2010-05-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2010-06-30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ingela Carlström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jakob Wilhelmsson, Lars-Erik Eknäs</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135230479</t>
         </is>
       </c>
     </row>
@@ -1006,6 +1233,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59894-2022 artfynd.xlsx
+++ b/artfynd/A 59894-2022 artfynd.xlsx
@@ -1006,7 +1006,7 @@
         <v>135227137</v>
       </c>
       <c r="B5" t="n">
-        <v>108456</v>
+        <v>108458</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tommy Carlström, Ingela Carlström</t>
+          <t>Ingela Carlström, Tommy Carlström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1113,7 +1113,7 @@
         <v>135230479</v>
       </c>
       <c r="B6" t="n">
-        <v>101505</v>
+        <v>101507</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
